--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487137_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487137_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8803</v>
+        <v>4.4915</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6179</v>
+        <v>1.5388</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2625</v>
+        <v>2.9527</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7158</v>
+        <v>3.2751</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1475</v>
+        <v>3.2022</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5684</v>
+        <v>0.0728</v>
       </c>
       <c r="J2" t="n">
-        <v>2.562</v>
+        <v>3.3014</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0426</v>
+        <v>4.0104</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4805</v>
+        <v>-0.709</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1538</v>
+        <v>-0.0263</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8951</v>
+        <v>-0.8082</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0489</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R2" t="n">
-        <v>4.2462</v>
+        <v>4.0532</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4926</v>
+        <v>-0.5979</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8304</v>
+        <v>-0.0955</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3378</v>
+        <v>-0.5024</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2859</v>
+        <v>0.6562</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0856</v>
+        <v>1.228</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7997</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="3">
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2293</v>
+        <v>4.3875</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4984</v>
+        <v>2.6567</v>
       </c>
       <c r="F3" t="n">
         <v>1.7309</v>
@@ -688,10 +688,10 @@
         <v>3.2811</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6081</v>
+        <v>-0.2337</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1845</v>
+        <v>0.3428</v>
       </c>
       <c r="U3" t="n">
         <v>-0.5764</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2095</v>
+        <v>4.0034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.578</v>
+        <v>1.8748</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6315</v>
+        <v>2.1286</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2751</v>
+        <v>2.7158</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2022</v>
+        <v>2.1475</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0728</v>
+        <v>0.5684</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3014</v>
+        <v>2.562</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0104</v>
+        <v>3.0426</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.709</v>
+        <v>-0.4805</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0263</v>
+        <v>0.1538</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8082</v>
+        <v>-0.8951</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7818000000000001</v>
+        <v>1.0489</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R4" t="n">
-        <v>4.0532</v>
+        <v>4.2462</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8798</v>
+        <v>0.6157</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0562</v>
+        <v>1.0874</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8236</v>
+        <v>-0.4717</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>1.228</v>
+        <v>2.0856</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5717</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2413</v>
+        <v>1.5943</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6634</v>
+        <v>2.1234</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4221</v>
+        <v>-0.5292</v>
       </c>
       <c r="G5" t="n">
         <v>0.6878</v>
@@ -844,13 +844,13 @@
         <v>2.8951</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4574</v>
+        <v>-0.1044</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2102</v>
+        <v>0.2499</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2472</v>
+        <v>-0.3543</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8842</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5047</v>
+        <v>0.6713</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4517</v>
+        <v>-0.1513</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9564</v>
+        <v>0.8225</v>
       </c>
       <c r="G6" t="n">
         <v>2.7711</v>
@@ -922,13 +922,13 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2664</v>
+        <v>-0.0998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0284</v>
+        <v>-0.1623</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0678</v>
+        <v>0.3216</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.414</v>
+        <v>-0.2137</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4818</v>
+        <v>0.5353</v>
       </c>
       <c r="G7" t="n">
         <v>0.1656</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4838</v>
+        <v>-0.23</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3649</v>
+        <v>-0.3113</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0113</v>
+        <v>-1.4575</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6506999999999999</v>
+        <v>-2.4216</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.662</v>
+        <v>0.9641</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2217</v>
+        <v>0.0354</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5309</v>
+        <v>-0.1324</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3092</v>
+        <v>0.1678</v>
       </c>
       <c r="J8" t="n">
-        <v>1.543</v>
+        <v>-0.3785</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2988</v>
+        <v>0.2484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2442</v>
+        <v>-0.6269</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3213</v>
+        <v>0.4139</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7679</v>
+        <v>-0.3808</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5534</v>
+        <v>0.7947</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6319</v>
+        <v>-0.23</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0378</v>
+        <v>-0.113</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4059</v>
+        <v>-0.117</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8999</v>
+        <v>-1.842</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8999</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.501</v>
+        <v>-1.6656</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4829</v>
+        <v>0.0499</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0181</v>
+        <v>-1.7155</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3656</v>
+        <v>0.2217</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1489</v>
+        <v>0.5309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7833</v>
+        <v>-0.3092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1685</v>
+        <v>1.543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0464</v>
+        <v>1.2988</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>0.2442</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5341</v>
+        <v>-1.3213</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1953</v>
+        <v>-0.7679</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6612</v>
+        <v>-0.5534</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1276</v>
+        <v>-0.0225</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0278</v>
+        <v>0.4369</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0998</v>
+        <v>-0.4594</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.842</v>
+        <v>-0.8999</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1278</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1714</v>
+        <v>-1.6796</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0819</v>
+        <v>0.0759</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9105</v>
+        <v>-1.7555</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0354</v>
+        <v>1.2649</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1324</v>
+        <v>-0.4802</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1678</v>
+        <v>1.7451</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3785</v>
+        <v>1.4644</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2484</v>
+        <v>-0.4399</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6269</v>
+        <v>1.9043</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4139</v>
+        <v>-0.1995</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3808</v>
+        <v>-0.0403</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7947</v>
+        <v>-0.1592</v>
       </c>
       <c r="P10" t="n">
-        <v>0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9439</v>
+        <v>-0.5308</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7733</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1706</v>
+        <v>-0.4584</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.842</v>
+        <v>-2.4137</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.842</v>
+        <v>-3.0277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5679</v>
+        <v>-1.6884</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.625</v>
+        <v>-0.4829</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9429</v>
+        <v>-1.2055</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2649</v>
+        <v>-0.3656</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4802</v>
+        <v>-1.1489</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7451</v>
+        <v>0.7833</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4644</v>
+        <v>0.1685</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4399</v>
+        <v>0.0464</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9043</v>
+        <v>0.1221</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1995</v>
+        <v>-0.5341</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0403</v>
+        <v>-1.1953</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1592</v>
+        <v>0.6612</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0.579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4191</v>
+        <v>-0.0598</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7733</v>
+        <v>0.0278</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6458</v>
+        <v>-0.0876</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4137</v>
+        <v>-1.842</v>
       </c>
       <c r="W11" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0277</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7507</v>
+        <v>-3.5504</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2808</v>
+        <v>-1.0805</v>
       </c>
       <c r="F12" t="n">
         <v>-2.4699</v>
@@ -1390,10 +1390,10 @@
         <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.267</v>
+        <v>-0.0668</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.2003</v>
       </c>
       <c r="U12" t="n">
         <v>-0.267</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.130600000000001</v>
+        <v>5.428100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6721</v>
+        <v>3.9695</v>
       </c>
       <c r="F13" t="n">
-        <v>1.458600000000001</v>
+        <v>1.458500000000001</v>
       </c>
       <c r="G13" t="n">
         <v>15.3846</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2419</v>
+        <v>5.241899999999999</v>
       </c>
       <c r="I13" t="n">
         <v>10.1426</v>
@@ -1447,19 +1447,19 @@
         <v>10.7523</v>
       </c>
       <c r="L13" t="n">
-        <v>4.9305</v>
+        <v>4.930499999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-0.2981000000000003</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.510400000000001</v>
+        <v>-5.5104</v>
       </c>
       <c r="O13" t="n">
         <v>5.2121</v>
       </c>
       <c r="P13" t="n">
-        <v>4.825199999999999</v>
+        <v>4.8252</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3358</v>
@@ -1468,10 +1468,10 @@
         <v>23.1609</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8572</v>
+        <v>-1.56</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9105</v>
+        <v>2.208</v>
       </c>
       <c r="U13" t="n">
         <v>-3.7678</v>
@@ -1480,7 +1480,7 @@
         <v>-13.2219</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4149</v>
+        <v>4.414899999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-17.6366</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8583</v>
+        <v>2.3458</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4795</v>
+        <v>1.9954</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6212</v>
+        <v>0.3503</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4013</v>
+        <v>-2.7048</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0361</v>
+        <v>-0.3828</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6348</v>
+        <v>-2.322</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8089</v>
+        <v>0.2719</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0764</v>
+        <v>1.7542</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7326</v>
+        <v>-1.4823</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4076</v>
+        <v>-2.9767</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0403</v>
+        <v>-2.137</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3674</v>
+        <v>-0.8397</v>
       </c>
       <c r="P14" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9301</v>
+        <v>3.2811</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6147</v>
+        <v>-0.1897</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3498</v>
+        <v>0.2978</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.735</v>
+        <v>-0.4875</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1228</v>
+        <v>3.8892</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>3.3558</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4087</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8495</v>
+        <v>1.8561</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3421</v>
+        <v>1.242</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5074</v>
+        <v>0.6141</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5275</v>
@@ -1624,13 +1624,13 @@
         <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2346</v>
+        <v>0.2413</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3385</v>
+        <v>0.2383</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1038</v>
+        <v>0.0029</v>
       </c>
       <c r="V15" t="n">
         <v>0.9843</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9994</v>
+        <v>1.6448</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8158</v>
+        <v>2.079</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1836</v>
+        <v>-0.4342</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1047</v>
+        <v>0.4013</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5393</v>
+        <v>1.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.644</v>
+        <v>-0.6348</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5303</v>
+        <v>1.8089</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4075</v>
+        <v>1.0764</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9378</v>
+        <v>0.7326</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5744</v>
+        <v>-1.4076</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8682</v>
+        <v>-0.0403</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7062</v>
+        <v>-1.3674</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1362</v>
+        <v>0.4012</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2062</v>
+        <v>0.9492</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3424</v>
+        <v>-0.548</v>
       </c>
       <c r="V16" t="n">
-        <v>2.6613</v>
+        <v>-0.1228</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0699</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
         <v>-0.4087</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6021</v>
+        <v>1.4403</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8939</v>
+        <v>1.0161</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2918</v>
+        <v>0.4242</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7048</v>
+        <v>-2.1047</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3828</v>
+        <v>0.5393</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.322</v>
+        <v>-2.644</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2719</v>
+        <v>-0.5303</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7542</v>
+        <v>1.4075</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4823</v>
+        <v>-1.9378</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9767</v>
+        <v>-1.5744</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.137</v>
+        <v>-0.8682</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8397</v>
+        <v>-0.7062</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2811</v>
+        <v>2.5091</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9334</v>
+        <v>0.3047</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8037</v>
+        <v>0.4065</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1296</v>
+        <v>-0.1018</v>
       </c>
       <c r="V17" t="n">
-        <v>3.8892</v>
+        <v>2.6613</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3558</v>
+        <v>3.0699</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5334</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5708</v>
+        <v>-0.043</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4055</v>
+        <v>1.6044</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8348</v>
+        <v>-1.6474</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2945</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2513</v>
+        <v>0.6375</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5269</v>
+        <v>0.7258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2756</v>
+        <v>-0.0883</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.901</v>
+        <v>-1.9615</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.087</v>
+        <v>-0.9869</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.9746</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6349</v>
@@ -1936,13 +1936,13 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4733</v>
+        <v>0.4128</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3993</v>
+        <v>0.4994</v>
       </c>
       <c r="U19" t="n">
-        <v>0.074</v>
+        <v>-0.0866</v>
       </c>
       <c r="V19" t="n">
         <v>1.9628</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1547</v>
+        <v>-1.9944</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4189</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7357</v>
+        <v>-1.5755</v>
       </c>
       <c r="G20" t="n">
         <v>-4.6921</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1514</v>
+        <v>0.3117</v>
       </c>
       <c r="T20" t="n">
         <v>0.2195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="V20" t="n">
         <v>1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.955</v>
+        <v>-7.7511</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.8894</v>
+        <v>-7.9895</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9344</v>
+        <v>0.2384</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8274</v>
@@ -2092,13 +2092,13 @@
         <v>2.7021</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2017</v>
+        <v>0.4055</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5315</v>
+        <v>0.4313</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6702</v>
+        <v>-0.0258</v>
       </c>
       <c r="V21" t="n">
         <v>2.619</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1306</v>
+        <v>-4.463</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.458500000000001</v>
+        <v>-1.4584</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6721</v>
+        <v>-3.0047</v>
       </c>
       <c r="G22" t="n">
         <v>-15.3846</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.242000000000001</v>
+        <v>-5.242</v>
       </c>
       <c r="I22" t="n">
         <v>-10.1427</v>
@@ -2146,10 +2146,10 @@
         <v>0.2979999999999992</v>
       </c>
       <c r="K22" t="n">
-        <v>5.5104</v>
+        <v>5.510400000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.212199999999999</v>
+        <v>-5.2122</v>
       </c>
       <c r="M22" t="n">
         <v>-15.6825</v>
@@ -2161,7 +2161,7 @@
         <v>-4.930400000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.825300000000001</v>
+        <v>-4.8253</v>
       </c>
       <c r="Q22" t="n">
         <v>-23.1609</v>
@@ -2170,13 +2170,13 @@
         <v>18.3358</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8574</v>
+        <v>2.525</v>
       </c>
       <c r="T22" t="n">
-        <v>3.768</v>
+        <v>3.7678</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.9103</v>
+        <v>-1.2429</v>
       </c>
       <c r="V22" t="n">
         <v>13.2218</v>
